--- a/AAII_Financials/Quarterly/AZO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AZO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="92">
   <si>
     <t>AZO</t>
   </si>
@@ -656,523 +656,535 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46151</v>
+      </c>
+      <c r="E7" s="2">
         <v>46067</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45983</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45899</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45787</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45703</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45619</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45535</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45416</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45332</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45248</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45052</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44968</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44884</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44800</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44688</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44604</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44520</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44436</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44324</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44240</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44156</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44072</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43960</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43876</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43792</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43708</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43589</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43505</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43421</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43337</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43225</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43141</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43057</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42973</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42861</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42777</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42693</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42609</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4841000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4274100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4628600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6242700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4464300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3952000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4279600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6205400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4235500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3859100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4190300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4090500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3691000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3985100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5348400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3865200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3369800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3668900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4913500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3651000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2910800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3154300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4546000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2779300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2513700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2793000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3988400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2783000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2450600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2641700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3558800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2660200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2413000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2589100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3512600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2619000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2289200</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2467800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>3398800</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2316400</v>
+      </c>
+      <c r="E9" s="3">
         <v>2030700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2269300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3026200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2110800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1823600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2011600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2947500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1970000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1779500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1976300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1944400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1761000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1990400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2592500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1858800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1584500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1743700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2345600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1736100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1351400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1478600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2133000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1288700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1147600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1292000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1858000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1291000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1125500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1224300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1650900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1237200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1136000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1223300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1658500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1240600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1083700</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1166300</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1604000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2524600</v>
+      </c>
+      <c r="E10" s="3">
         <v>2243400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2359300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3216500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2353500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2128400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2268100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3257900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2265500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2079700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2214000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2146100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1930000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1994700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2755900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2006400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1785300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1925200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2567900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1914900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1559400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1675700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2413000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1490600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1366100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1501000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2130400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1492000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1325100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1417400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1907900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1423000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1277000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1365800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1854100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1378400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1205500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1301500</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1794800</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1214,8 +1226,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1333,8 +1346,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1452,8 +1468,11 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1508,27 +1527,27 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>-3000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>6100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>39900</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>8900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>75000</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1541,8 +1560,8 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1571,50 +1590,53 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>160300</v>
+      </c>
+      <c r="E15" s="3">
         <v>155600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>148200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>197400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>144700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>137900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>133200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>175300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>129200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>125000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>120200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>116100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>113700</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1633,8 +1655,8 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>8</v>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>8</v>
@@ -1651,47 +1673,50 @@
       <c r="AB15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AC15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD15" s="3">
         <v>118800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>84900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>83800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>82500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>108000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>79800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>79400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>78000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>103100</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>75300</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>72800</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>71800</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>93900</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1730,246 +1755,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3917200</v>
+      </c>
+      <c r="E17" s="3">
         <v>3575600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3844400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5046700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3598200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3245200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3438500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4908700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3335300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3115900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3341700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3232100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3021000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3262000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4244500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3079600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2743000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2914400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3869500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2847500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2429100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2539000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3527900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2287600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2105700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2293000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3207700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2235500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2050500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2153900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2967500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2114400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2207900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2120400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2805000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2089400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1905300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2008900</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2695400</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>923800</v>
+      </c>
+      <c r="E18" s="3">
         <v>698500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>784200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1196100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>866200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>706800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>841100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1296700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>900200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>743200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>848600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>858500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>670000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>723100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1103900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>785600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>626800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>754500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1044000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>803500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>481700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>615300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1018100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>491700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>408000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>500000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>780700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>547500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>400100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>487800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>591300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>545800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>205100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>468700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>707600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>529600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>384000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>458900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>703400</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2011,8 +2043,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2052,249 +2085,255 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-57800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-64000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-41900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-42500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-43300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-58100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-45000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-45300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-45500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-64900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-46500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-43100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-42300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-61200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-43200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-41400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-39000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-54400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-42000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-39300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-38900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-51400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-35700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-34200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-33300</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-45800</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1084000</v>
+      </c>
+      <c r="E21" s="3">
         <v>854100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>932400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1393500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1010900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>844700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>974300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1472000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1029400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>868200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>968800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>974600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>783700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>774600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1180700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>845900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>684000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>810800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1115500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>852500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>530900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>659300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1078500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>536900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>455600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>547400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>838400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>589200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>442400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>531300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>644900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>583600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>245100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>507900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>759300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>569200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>422600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>497400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>751500</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>110500</v>
+      </c>
+      <c r="E22" s="3">
         <v>107200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>106300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>159100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>111300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>108800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>107600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>164500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>104400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>102600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>91400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>74300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>65600</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>8</v>
@@ -2311,27 +2350,27 @@
       <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W22" s="3">
-        <v>700</v>
+      <c r="W22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X22" s="3">
         <v>700</v>
       </c>
       <c r="Y22" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z22" s="3">
         <v>800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1400</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2347,8 +2386,8 @@
       <c r="AH22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI22" s="3">
-        <v>0</v>
+      <c r="AI22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ22" s="3">
         <v>0</v>
@@ -2368,246 +2407,255 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>813300</v>
+      </c>
+      <c r="E23" s="3">
         <v>591300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>677900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1048000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>754900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>597900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>733500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1143500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>795800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>640600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>757200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>784200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>604400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>665300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1039800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>743800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>584300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>711200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>985900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>758500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>435800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>569000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>952400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>444200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>363600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>456300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>719600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>504300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>358700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>448800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>536900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>503800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>165800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>429900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>656200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>493900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>349800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>425600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>657600</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>171800</v>
+      </c>
+      <c r="E24" s="3">
         <v>122400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>147100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>211000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>146400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>110000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>168600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>241300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>144000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>125600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>163800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>136400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>127800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>126000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>229800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>151200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>112500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>156000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>200100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>162300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>89800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>126600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>212000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>101300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>64300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>105900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>51300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>201400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>72800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>97400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>156800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>136500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>47600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>148900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>222300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>162200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>112600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>147500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>230800</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2725,246 +2773,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>641500</v>
+      </c>
+      <c r="E26" s="3">
         <v>468900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>530800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>837000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>608400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>487900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>564900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>902200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>651700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>515000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>593500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>647700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>476500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>539300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>810000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>592600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>471800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>555200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>785800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>596200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>345900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>442400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>740500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>342900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>299300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>350300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>668300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>302800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>285800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>351400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>380100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>367300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>118100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>281000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>433900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>331700</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>237100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>278100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>426800</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>641500</v>
+      </c>
+      <c r="E27" s="3">
         <v>468900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>530800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>837000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>608400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>487900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>564900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>902200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>651700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>515000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>593500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>647700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>476500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>539300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>810000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>592600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>471800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>555200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>785800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>596200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>345900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>442400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>740500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>342900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>299300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>350300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>668300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>302800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>285800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>351400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>380100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>367300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>118100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>281000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>433900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>331700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>237100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>278100</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>426800</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3082,8 +3139,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3144,8 +3204,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -3162,30 +3222,30 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-103100</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>103100</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>8800</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>20200</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-600</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>171400</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3201,8 +3261,11 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3320,8 +3383,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3439,8 +3505,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3480,205 +3549,211 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="3">
         <v>57800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>64000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>41900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>42500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>43300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>58100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>45000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>45300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>45500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>64900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>46500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>43100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>42300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>61200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>43200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>41400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>39000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>54400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>42000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>39300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>38900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>51400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>35700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>34200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>33300</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>641500</v>
+      </c>
+      <c r="E33" s="3">
         <v>468900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>530800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>837000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>608400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>487900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>564900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>902200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>651700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>515000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>593500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>647700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>476500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>539300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>810000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>592600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>471800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>555200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>785800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>596200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>345900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>442400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>740500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>342900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>299300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>350300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>565200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>405900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>294600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>351400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>400300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>366700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>289500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>281000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>433900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>331700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>237100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>278100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>426800</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3796,251 +3871,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>641500</v>
+      </c>
+      <c r="E35" s="3">
         <v>468900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>530800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>837000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>608400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>487900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>564900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>902200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>651700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>515000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>593500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>647700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>476500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>539300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>810000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>592600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>471800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>555200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>785800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>596200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>345900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>442400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>740500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>342900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>299300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>350300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>565200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>405900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>294600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>351400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>400300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>366700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>289500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>281000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>433900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>331700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>237100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>278100</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>426800</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46151</v>
+      </c>
+      <c r="E38" s="2">
         <v>46067</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45983</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45899</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45787</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45703</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45619</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45535</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45416</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45332</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45248</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45052</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44968</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44884</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44800</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44688</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44604</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44520</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44436</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44324</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44240</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44156</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44072</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43960</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43876</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43792</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43708</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43589</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43505</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43421</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43337</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43225</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43141</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43057</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42973</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42861</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42777</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42693</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42609</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4082,8 +4166,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4125,169 +4210,173 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>253700</v>
+      </c>
+      <c r="E41" s="3">
         <v>285500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>287600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>271800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>268600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>300900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>304000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>298200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>275400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>304100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>283000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>274900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>301300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>269800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>264400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>263000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>239400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>961100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1171300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>975600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1026200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1664000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1750800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>509100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>153000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>158100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>176300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>174100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>195700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>252100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>217800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>218400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>288500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>257700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>293300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>227100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>210600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>195500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>189700</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E42" s="3">
         <v>28500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>21700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>18700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>19000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>28800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>34300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>38400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>60600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>53300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>50400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>42600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>62500</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4363,526 +4452,541 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>764900</v>
+      </c>
+      <c r="E43" s="3">
         <v>698400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>637800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>670100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>588500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>597400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>533500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>545600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>586800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>501100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>511900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>471000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>484800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>501800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>504900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>439800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>405600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>379300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>378400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>359700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>352500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>350900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>364800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>266900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>340300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>333200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>309000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>281600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>298300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>275200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>258100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>261300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>282500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>272500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>280700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>276100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>246900</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>270800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>287700</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7559100</v>
+      </c>
+      <c r="E44" s="3">
         <v>7484000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7144400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7025700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6822900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6588600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6274100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6155200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6155300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5970200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5774500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5703700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5731300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5607700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5638000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5313100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5031200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4768300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4639800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4665500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4736800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4628300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4473300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4440600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4606200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4463100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4319100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4325700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4305500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4090400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3943700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4005800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4085500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4012100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>3882100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>3861100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>3902100</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>3773200</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>3631900</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>340100</v>
+      </c>
+      <c r="E45" s="3">
         <v>335700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>351000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>355100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>286700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>286900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>274600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>269400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>211400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>328400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>337000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>216700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>215000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>253800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>220700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>238700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>227500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>240500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>225800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>223600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>211300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>193500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>223000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>181400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>201100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>202500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>224300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>190000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>197600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>196700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>216200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>185800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>169700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>175000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>155200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>142900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>133100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>129100</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>130200</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8934600</v>
+      </c>
+      <c r="E46" s="3">
         <v>8832100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8442500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8341400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7985700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7802600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7420600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7306800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7289500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7157100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6956800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6708900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6794800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6633100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6628000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6254700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5903800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6349100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6415300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6224400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6326800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6836800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6811900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5398000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5300500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5157000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5028700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4971300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4997100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4814300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4635900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4671300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4826300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4717200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4611300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>4507200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>4492800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4368700</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>4239600</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>195100</v>
+      </c>
+      <c r="E47" s="3">
         <v>182000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>173300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>166300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>206400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>184600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>171200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>137600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>58400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>70900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>73600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>81900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>60500</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -4958,127 +5062,133 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11211000</v>
+      </c>
+      <c r="E48" s="3">
         <v>10854700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10487600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10257200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9872800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9570000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9368000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9241300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9146100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8906800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8711800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8293500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8180000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8116700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8089200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7736300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7622900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7575500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7575600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7378000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7288700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7193000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7090900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6998400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7055600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7035800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4398800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4324900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4269900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4228800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4218400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4123000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>4081300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>4061000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>4031000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3904200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>3803800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>3750500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>3733300</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5146,58 +5256,61 @@
         <v>302600</v>
       </c>
       <c r="Y49" s="3">
+        <v>302600</v>
+      </c>
+      <c r="Z49" s="3">
         <v>304100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>305400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>306300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>307300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>308300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>309500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>310500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>311500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>312400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>324800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>326700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>443000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>444400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>447000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>448900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>450900</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>452900</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5315,8 +5428,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5434,127 +5550,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>100600</v>
+      </c>
+      <c r="E52" s="3">
         <v>100900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>105300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>139800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>136400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>159200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>124000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>104500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>226500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>195600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>163600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>148900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>147400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>263500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>255200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>226900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>249200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>233700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>222600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>232900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>241800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>236100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>217000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>200300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>201200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>200400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>160200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>167900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>167600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>169000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>180300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>182700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>169400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>176000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>173100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>169900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>157200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>172500</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5672,127 +5794,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20916500</v>
+      </c>
+      <c r="E54" s="3">
         <v>20438600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19665600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19355300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>18622000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18116300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17465800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17176500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17108400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16717700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16292600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15597900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15545100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15315900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15275000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>14520600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14078500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14460900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14516200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14137900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>14160000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>14568600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>14423900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>12902100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12863700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12700500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9895900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>9773700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>9745100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>9523600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>9347000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>9301800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>9403700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>9397100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>9259800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>9028300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>8902600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>8742500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>8599800</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5834,8 +5962,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5877,208 +6006,212 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8401300</v>
+      </c>
+      <c r="E57" s="3">
         <v>8297500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8262300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8025600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7887400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7784700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7498700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7355700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7369700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7149900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7182900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7215600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7321600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7346000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7301300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6793200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6378600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6171300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6013900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5778200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5351100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5282300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5156300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4806300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4869900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4922100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4864900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4693100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4669600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4455300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4409400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4296700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4365700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>4326700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>4168900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>4140700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>4115000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>4162300</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>4095900</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>336300</v>
+      </c>
+      <c r="E58" s="3">
         <v>329100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>287200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>395100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>314900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>306200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>270100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>382400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>803200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>296500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>288900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>282000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>275300</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q58" s="3">
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R58" s="3">
         <v>92900</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U58" s="3">
         <v>500000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>89900</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X58" s="3">
         <v>314500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>63400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>67500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>58000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>58900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>57800</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD58" s="3" t="s">
         <v>8</v>
       </c>
@@ -6094,8 +6227,8 @@
       <c r="AH58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI58" s="3">
-        <v>0</v>
+      <c r="AI58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ58" s="3">
         <v>0</v>
@@ -6115,484 +6248,499 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>70900</v>
+      </c>
+      <c r="E59" s="3">
         <v>72300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>58900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>372100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>167300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>152600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>85500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>297600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>30300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>111200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>111300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>61000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>84100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1363000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1194200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1270900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1306000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1416500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1265900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1235000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1138700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1111000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1059300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>904700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>850800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>888300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>647200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>623800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>664700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>712800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>619300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>621700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>581600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>740900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>597400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>652900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>669300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>687900</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>594500</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10035300</v>
+      </c>
+      <c r="E60" s="3">
         <v>9921200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9813900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9519400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9465500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9267400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8888600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8714200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9192600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8772600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8785600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8464900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8614600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8709000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8588400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8064100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7684600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8087900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7369800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7013200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6804300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6456700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6283100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5769100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5779600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5868200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5512100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5316900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5334300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5168200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5028700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4918300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4947200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5067600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>4766300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>4793500</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>4784300</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>4850200</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>4690300</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12750200</v>
+      </c>
+      <c r="E61" s="3">
         <v>12514500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12135900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12182100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12281300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12445500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12384400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12268400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11804300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11861100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11494300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10202600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9896500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6328300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6339500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6057400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5840900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4771300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5455900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5267900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5427300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5684400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5669200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5544500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5588700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5425200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5206300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5151900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5111200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5156000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5005900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>4954700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5043500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>4983000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5081200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>5152800</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>5151900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>4997400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>4924100</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>431800</v>
+      </c>
+      <c r="E62" s="3">
         <v>407500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>412200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>547600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>437200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>386000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>369700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>496400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>406800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>381300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>691900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>693700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>682100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4116500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3886000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3786300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3690400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3726500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3488000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3620200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3451900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3454500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3349500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3221300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3206700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3183100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>891300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>894400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>894000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>858000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>832700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>790300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>743500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>871600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>840600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>796100</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>793900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>790100</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>772900</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6710,8 +6858,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6829,8 +6980,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6948,127 +7102,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23701000</v>
+      </c>
+      <c r="E66" s="3">
         <v>23347400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>22894200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>22769600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>22596400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>22574100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>22138700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>21926200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>21946700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>21555000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>21506200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19899500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19729300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19153900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18814000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>17907800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>17216000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>16585700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>16313700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>15901300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15683600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15595600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>15301800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>14534900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>14574900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>14476500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>11609800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>11363300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>11339500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>11182200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>10867300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>10663400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>10734300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>10922200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>10688200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>10742500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>10730100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>10637800</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>10387300</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7110,8 +7270,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7229,8 +7390,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7348,8 +7512,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7467,8 +7634,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7586,127 +7756,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3750100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-4391600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3445000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3975900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-4812800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-5421200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3860000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-4425000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-5327200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-5978900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2365800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3824100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-4471800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-790700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1330100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2138200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-2730700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>135400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-419800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1205600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1801800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1008500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1451000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-2191400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-2534300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-955000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-1305300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-1870600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-2276500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-864200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-1208800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-1623600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-1990300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-1361400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-1642400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-2076300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-2408000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-1324100</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-1602200</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7824,8 +8000,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7943,8 +8122,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8062,127 +8244,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2784600</v>
+      </c>
+      <c r="E76" s="3">
         <v>-2908800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-3228600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-3414300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-3974400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-4457800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-4672900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-4749600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-4838200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-4837300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-5213700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-4301600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-4184200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-3837900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-3538900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-3387200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-3137500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-2124800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-1797500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-1763400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-1523600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-1027000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-878000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-1632700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-1711100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-1776100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-1713900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-1589500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-1594400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-1658600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-1520400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-1361600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-1330500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>-1525100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>-1428400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>-1714200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>-1827400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>-1895200</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>-1787500</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8300,251 +8488,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46151</v>
+      </c>
+      <c r="E80" s="2">
         <v>46067</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45983</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45899</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45787</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45703</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45619</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45535</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45416</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45332</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45248</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45052</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44968</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44884</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44800</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44688</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44604</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44520</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44436</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44324</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44240</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44156</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44072</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43960</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43876</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43792</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43708</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43589</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43505</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43421</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43337</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43225</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43141</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43057</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42973</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42861</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42777</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42693</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42609</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>641500</v>
+      </c>
+      <c r="E81" s="3">
         <v>468900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>530800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>837000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>608400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>487900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>564900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>902200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>651700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>515000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>593500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>647700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>476500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>539300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>810000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>592600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>471800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>555200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>785800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>596200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>345900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>442400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>740500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>342900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>299300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>350300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>565200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>405900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>294600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>351400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>400300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>366700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>289500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>281000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>433900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>331700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>237100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>278100</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>426800</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8586,127 +8783,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>144700</v>
+      </c>
+      <c r="E83" s="3">
         <v>137900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>133200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>175300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>129200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>125000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>120200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>158500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>116100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>113700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>109300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>102100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>99700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>109300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>140900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>102100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>99700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>99600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>129600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>94000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>94500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>89600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>125400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>91700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>90700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>89800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>118800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>84900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>83800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>82500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>108000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>79800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>79400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>78000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>103100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>75300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>72800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>71800</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>93900</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8824,8 +9025,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8943,8 +9147,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9062,8 +9269,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9181,8 +9391,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9300,127 +9513,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>802000</v>
+      </c>
+      <c r="E89" s="3">
         <v>373400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>944200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>952800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>769000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>583700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>811800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1070300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>669500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>434100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>830300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>724700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>354500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>793600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1228000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>843400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>361800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>777900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1288200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1190500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>356400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>683500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1417000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>651500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>204500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>447100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>841900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>469600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>367900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>449200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>823900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>504000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>187300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>565000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>561400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>445300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>157400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>406500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>545800</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9462,127 +9681,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-345500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-337800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-314200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-441600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-345900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-292700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-247000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-346800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-235100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-255400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-235400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-171200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-144800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-114400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-303000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-161200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-105900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-102300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-246100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-373700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-183800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-83300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-89200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-101400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-182200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-118000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-97700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-98200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>326700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-112400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-104500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-110300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-195900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-141800</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-118200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-97900</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-377700</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9700,8 +9923,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9819,127 +10045,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-345600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-340800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-326700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-483200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-353800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-297700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-265700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-370200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-372300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-273500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-270500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-209000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-156100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-113900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-287400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-149400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-120400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-91000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-243100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-130300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-118200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-110200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-250000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-73000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-84200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-90700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-206600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-109100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-84300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-91900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-219200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-72100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-96000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-134700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-194400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-156500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-103100</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-99700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-189500</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9981,8 +10213,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10022,8 +10255,8 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10100,8 +10333,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10219,8 +10455,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10338,8 +10577,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10457,361 +10699,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-487700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-40200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-602700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-469000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-451300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-288400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-538100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-664800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-326100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-140600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-552200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-543600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-169100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-675700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-939700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-670900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-964000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-895900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-849200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1110400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-877400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-663400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>68500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-209400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-127000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-375800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-630600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-381900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-345900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-315600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-607000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-500900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-60600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-463700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-302500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-275300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-38600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-297900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-363800</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-12400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>3300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>6100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-12900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>5900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-7400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>1600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>3000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-600</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-3100</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>15800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-32300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>22800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-28700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>21100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-26400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>31500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>23600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-721700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-210200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>195700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-50500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-637800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-86800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1241700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>356100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-18200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>2200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-21600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-56400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>34300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-70100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>30800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-35600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>66100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>16500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>15100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>5800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-23600</v>
       </c>
     </row>
